--- a/nr-update-dependency/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-update-dependency/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T12:05:38+00:00</t>
+    <t>2024-04-23T12:06:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
